--- a/01_Thermal/B_results/four_annular_bemt_params.xlsx
+++ b/01_Thermal/B_results/four_annular_bemt_params.xlsx
@@ -679,136 +679,136 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3079704946776221</v>
+        <v>0.3070871685863056</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2321305976309831</v>
+        <v>0.2329940927529772</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>100.0212583092712</v>
+        <v>110.6049197342154</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0655898623305452</v>
+        <v>-0.06842895636174645</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2998031130945062</v>
+        <v>0.3001362884761485</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1704155742467602</v>
+        <v>0.1699654550637675</v>
       </c>
       <c r="K2" t="n">
-        <v>7.711062747169664</v>
+        <v>7.698296625876307</v>
       </c>
       <c r="L2" t="n">
-        <v>1.23443724081681</v>
+        <v>1.227554585639528</v>
       </c>
       <c r="M2" t="n">
-        <v>1.253156872788088</v>
+        <v>1.24614447181849</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7962499621197922</v>
+        <v>-0.7961853351143451</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0006305764357821911</v>
+        <v>0.0144241030577102</v>
       </c>
       <c r="P2" t="n">
-        <v>0.01928698619686466</v>
+        <v>0.02239733392807139</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2915114932374239</v>
+        <v>0.2917410565696216</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1610878803235903</v>
+        <v>0.1605031521305101</v>
       </c>
       <c r="S2" t="n">
         <v>8.044499999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3510557013603043</v>
+        <v>-0.3520157995638803</v>
       </c>
       <c r="U2" t="n">
-        <v>1.872576305113732</v>
+        <v>1.875215550250575</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.05183291548313045</v>
+        <v>-0.05191301037765998</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.9906239470873</v>
+        <v>-1.985262479644983</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1749337391942141</v>
+        <v>0.1784362989155303</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2937228438474765</v>
+        <v>0.2944144400703275</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1630021165201194</v>
+        <v>0.1616404017315249</v>
       </c>
       <c r="AA2" t="n">
         <v>9.100250000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.586484168621923</v>
+        <v>1.578903461170347</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.148153606274984</v>
+        <v>1.145601909398014</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.7612219062732427</v>
+        <v>-0.7627995608634331</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.2015851154317049</v>
+        <v>-0.35323621614967</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1794097946631991</v>
+        <v>0.1827903683534494</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.2983370132949946</v>
+        <v>0.2986595139527869</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.1553925387975185</v>
+        <v>0.1546777428958966</v>
       </c>
       <c r="AI2" t="n">
         <v>8.354593749999998</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-1.81177390026329</v>
+        <v>-1.815268541960138</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.5210069085837047</v>
+        <v>0.5215832373007344</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1.044354558198022</v>
+        <v>-1.045682755365054</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.229186333552533</v>
+        <v>0.2250919973833315</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.07701016443093314</v>
+        <v>0.07879876120882615</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.2958436158686003</v>
+        <v>0.2962378247672212</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.1624745274719971</v>
+        <v>0.1616966879554247</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.302601624292416</v>
+        <v>8.299410093969076</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.1645229519537849</v>
+        <v>0.159793426321464</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.198723423190127</v>
+        <v>1.197136292191953</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0.6634148355185467</v>
+        <v>-0.664145165430123</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.4909133263505635</v>
+        <v>-0.5247456488384029</v>
       </c>
     </row>
     <row r="3">
@@ -824,136 +824,136 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3633837736967366</v>
+        <v>0.5490400540866132</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2582408273116724</v>
+        <v>0.2880298744474953</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>147.1838355075075</v>
+        <v>157.8341079908381</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05944294019532716</v>
+        <v>0.04870439806472449</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2601810720960586</v>
+        <v>0.649999999999842</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5093215501104444</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>2.599478189312103</v>
+        <v>0.5260619256701073</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5787764230119408</v>
+        <v>-0.1895321978620723</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1626973005030835</v>
+        <v>-0.5192199233857774</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6494257136967313</v>
+        <v>-0.09147439392544279</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4210766907214771</v>
+        <v>0.06565522357566832</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01019627171037464</v>
+        <v>1.9186141825415e-05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3519335821868446</v>
+        <v>0.3509691552645023</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2668045540184604</v>
+        <v>0.2685048222262671</v>
       </c>
       <c r="S3" t="n">
-        <v>2.829165996468598</v>
+        <v>2.861329990464961</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1639967056172782</v>
+        <v>0.188313483819213</v>
       </c>
       <c r="U3" t="n">
-        <v>1.06602380994552</v>
+        <v>1.068207568454569</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8692970549351065</v>
+        <v>0.8629541558750187</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6629609289585763</v>
+        <v>-0.6775048646047581</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04396541586577573</v>
+        <v>0.032879926796039</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2981586484612423</v>
+        <v>0.2971995739471388</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2250216644416302</v>
+        <v>0.2253548110890088</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.534439724593332</v>
+        <v>4.521932101865637</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.405625519398187</v>
+        <v>2.392302151050057</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.44109583049364</v>
+        <v>-0.552402741438483</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.7162015230356514</v>
+        <v>-0.6866728036755009</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1.400577020491429</v>
+        <v>-1.605084993173607</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1233996525746793</v>
+        <v>0.1115245598798791</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3065647400201604</v>
+        <v>0.30585904841714</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2059084108073032</v>
+        <v>0.209028823955737</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.730791683684577</v>
+        <v>4.767838431922064</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.8059838671366482</v>
+        <v>0.8040014425619971</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.279435224078692</v>
+        <v>1.269839472774124</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.7011020062378398</v>
+        <v>-0.6995203656974418</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.2595142792792222</v>
+        <v>0.2617221742960592</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.05925107008653921</v>
+        <v>0.04828201772061699</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.3042095106910765</v>
+        <v>0.4010069444071557</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3017640448444596</v>
+        <v>0.4257221143177531</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.673468898514652</v>
+        <v>3.169290612480692</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.6992074172850431</v>
+        <v>0.7987712198922987</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.5167651260084138</v>
+        <v>0.3166060941011081</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.0253548098395866</v>
+        <v>-0.1536783518558417</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.5562750902230649</v>
+        <v>-0.4888031149766594</v>
       </c>
     </row>
     <row r="4">
@@ -969,136 +969,136 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4319136672312052</v>
+        <v>0.4301367971180799</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2741875245219532</v>
+        <v>0.2751283748604808</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>133.1722334368714</v>
+        <v>147.3765820468469</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03110434289223112</v>
+        <v>0.03195251585108323</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5293419582923392</v>
+        <v>0.530353276964896</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2017281864426674</v>
+        <v>0.1982377252665156</v>
       </c>
       <c r="K4" t="n">
-        <v>2.708036382087183</v>
+        <v>2.702335807052048</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7696241341503021</v>
+        <v>-0.7688965721173461</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6806369616628406</v>
+        <v>0.6421521201367134</v>
       </c>
       <c r="N4" t="n">
-        <v>0.932834555177863</v>
+        <v>1.003108128305951</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9242687732289112</v>
+        <v>-0.9254111613005507</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01491201443709331</v>
+        <v>0.01574686783800995</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5270665075603638</v>
+        <v>0.5268445675189075</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1708095984071791</v>
+        <v>0.1701482800039372</v>
       </c>
       <c r="S4" t="n">
-        <v>2.832719764645864</v>
+        <v>2.831774172988569</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.735601599222705</v>
+        <v>-1.738954794294159</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6348031820909377</v>
+        <v>0.6364772643415658</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.08731327736703032</v>
+        <v>-0.08865051959931765</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7418729614553835</v>
+        <v>-0.7424448671069743</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1053191815464883</v>
+        <v>0.1062284026969533</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.178818471683381</v>
+        <v>0.2014133603286974</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.484288820019997</v>
+        <v>0.4675518634689663</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.840062874309583</v>
+        <v>2.784449877990022</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2649176466042139</v>
+        <v>0.2830742588788154</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.5975736303354467</v>
+        <v>-0.5374606145208538</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.8516971471440846</v>
+        <v>0.8081309705386965</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.8916249752838907</v>
+        <v>-0.8225210843523818</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.07916728601445329</v>
+        <v>0.08005499494718549</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3508477376557848</v>
+        <v>0.3505921225656516</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.3476457558249963</v>
+        <v>0.3466393606972639</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.361651853963298</v>
+        <v>2.360270708022261</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.7804770682777371</v>
+        <v>0.783316351306331</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.002632158775703448</v>
+        <v>-0.003090774787603614</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.1190761026591954</v>
+        <v>-0.1184011054814306</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.1831484652760481</v>
+        <v>0.1844177269501827</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.05762570622256649</v>
+        <v>0.05849569533330798</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.3965186687979672</v>
+        <v>0.4023008318445381</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.3011180901737099</v>
+        <v>0.2956443073591707</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.685617718751482</v>
+        <v>2.669707641513225</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.3649577546227641</v>
+        <v>-0.3603651890565896</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.178808588660657</v>
+        <v>0.1845194987924554</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.3945355805739305</v>
+        <v>0.4010468684409748</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.5936545611730344</v>
+        <v>-0.5764898464524311</v>
       </c>
     </row>
     <row r="5">
@@ -1114,136 +1114,136 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3921456993921941</v>
+        <v>0.3896332152354891</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2721875175692376</v>
+        <v>0.2733502100677215</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>344.5834702291271</v>
+        <v>385.1806509287684</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.04893244417822781</v>
+        <v>-0.04697826742415452</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5846404405411784</v>
+        <v>0.5817449828792735</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1963803826998824</v>
+        <v>0.1987772928073513</v>
       </c>
       <c r="K5" t="n">
-        <v>2.576618085151863</v>
+        <v>2.571756514364463</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5900956052758345</v>
+        <v>0.5565046301214347</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4763727311980013</v>
+        <v>0.4686528063719399</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1188333820343054</v>
+        <v>-0.02356478191824077</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8881309768541548</v>
+        <v>-0.8857909858311381</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06377741438209251</v>
+        <v>0.06492484461452371</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5710846551943397</v>
+        <v>0.5705076840304724</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1832458515345434</v>
+        <v>0.182395619191287</v>
       </c>
       <c r="S5" t="n">
-        <v>3.023191916503707</v>
+        <v>3.017032011213016</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3024548669791078</v>
+        <v>-0.3019601829109342</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7785321715864993</v>
+        <v>0.7792059871203836</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.331307030641859</v>
+        <v>-0.332221102855063</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.361312944847829</v>
+        <v>-0.3611373218410147</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1464099170045084</v>
+        <v>0.1476464777551237</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3069350650430313</v>
+        <v>0.3054450463325407</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3803861044149847</v>
+        <v>0.3763310596894388</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.498066366709825</v>
+        <v>2.498908784840098</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.5144006146788049</v>
+        <v>-0.4675659321558129</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.1912643770409712</v>
+        <v>-0.1810597873812929</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.09850667892831513</v>
+        <v>0.09530073602988956</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.2180281637424094</v>
+        <v>-0.214878884257754</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2107054316862288</v>
+        <v>0.212011343987487</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.5381274433876168</v>
+        <v>0.5379096254521967</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.1980725592331016</v>
+        <v>0.1972662235239467</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.515896419870054</v>
+        <v>2.511611782912897</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.8155783260361964</v>
+        <v>0.8169395360281914</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.08717490759370365</v>
+        <v>-0.08800072176236755</v>
       </c>
       <c r="AL5" t="n">
-        <v>-1.746959676891481</v>
+        <v>-1.753006630734389</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.3524332902432759</v>
+        <v>-0.3524947890427977</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.09299007972365048</v>
+        <v>0.09440109973324498</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.5001969010415415</v>
+        <v>0.4989018346736208</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.239521224470628</v>
+        <v>0.238692548803006</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.653443197058862</v>
+        <v>2.649827273332618</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.1472046124135296</v>
+        <v>0.1509795127707197</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.2441164045374565</v>
+        <v>0.2446995710871658</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.5246483526598327</v>
+        <v>-0.5033729448694507</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.4549763439219173</v>
+        <v>-0.4535754952431761</v>
       </c>
     </row>
     <row r="6">
@@ -1259,136 +1259,136 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4124435253730828</v>
+        <v>0.4112383304357538</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2776547910717677</v>
+        <v>0.2782458734513925</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>195.8416713387924</v>
+        <v>221.6939679615793</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03390997701379776</v>
+        <v>0.03665619029436355</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3619369135014913</v>
+        <v>0.3640394263967048</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4710623902647759</v>
+        <v>0.4774798223261441</v>
       </c>
       <c r="K6" t="n">
-        <v>2.218977779650983</v>
+        <v>2.208653254787602</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4236621545407124</v>
+        <v>0.4125149002120131</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4532081322987415</v>
+        <v>0.4302977856868854</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02028731389594683</v>
+        <v>0.02455063375947884</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5447730273128549</v>
+        <v>0.499856442280173</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.07580744321056432</v>
+        <v>-0.085399255270665</v>
       </c>
       <c r="Q6" t="n">
         <v>0.15</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8666946893782382</v>
+        <v>0.8824688199124172</v>
       </c>
       <c r="S6" t="n">
-        <v>1.653481031400566</v>
+        <v>1.629271297174825</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6035741333233912</v>
+        <v>-0.6069085071965725</v>
       </c>
       <c r="U6" t="n">
-        <v>0.05213791052524083</v>
+        <v>0.05526145088512934</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4552762836632379</v>
+        <v>-0.438991577232705</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2281540192074949</v>
+        <v>-0.2363582224273399</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02807628356779163</v>
+        <v>0.03080700172900964</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5515042694567279</v>
+        <v>0.5465280015438483</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6282178825800814</v>
+        <v>0.6239619128410973</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.346173542059335</v>
+        <v>1.364526694067</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6945877911771454</v>
+        <v>0.6700703158203796</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.4950323434536064</v>
+        <v>0.5251348125286727</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.03505792972464911</v>
+        <v>-0.02999216641172034</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.2366170020920764</v>
+        <v>0.2232918977743206</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1483401176984663</v>
+        <v>0.1513902738501608</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.3489985759959687</v>
+        <v>0.3489121585824726</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.4008776479653534</v>
+        <v>0.4008811375997733</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.840448556949456</v>
+        <v>1.841418031077795</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.3766316641358483</v>
+        <v>0.3747489219859632</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.1639240770137277</v>
+        <v>-0.1669356908802885</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0944446860399064</v>
+        <v>-0.09242599838347854</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.4946829380612641</v>
+        <v>0.4953172160437589</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.03362973376737285</v>
+        <v>0.03336355265071725</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.353109939738547</v>
+        <v>0.3523698966307564</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.5917131525471122</v>
+        <v>0.596197923169858</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.764770227515085</v>
+        <v>1.760967319276805</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.2228268691325787</v>
+        <v>0.2126064077054458</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.2091135773159652</v>
+        <v>0.2109395895550998</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.1411228963829616</v>
+        <v>-0.1342147770671062</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.2619797370646751</v>
+        <v>0.2455268334177281</v>
       </c>
     </row>
     <row r="7">
@@ -1404,91 +1404,91 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2992163700952643</v>
+        <v>0.2986364560272359</v>
       </c>
       <c r="E7" t="n">
-        <v>0.204232652217948</v>
+        <v>0.2048135103805745</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>160.7569375819061</v>
+        <v>170.6804554918937</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2289635935819669</v>
+        <v>-0.08706105687677107</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4198343245193607</v>
+        <v>0.4120979837118133</v>
       </c>
       <c r="J7" t="n">
-        <v>0.479085000966217</v>
+        <v>0.4595598815840282</v>
       </c>
       <c r="K7" t="n">
-        <v>1.515208336959375</v>
+        <v>1.572691324659599</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2965213095090266</v>
+        <v>0.2191976539837004</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03187475052452852</v>
+        <v>0.02729360643842402</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3636499379533683</v>
+        <v>-0.4074809841003392</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0453764277161447</v>
+        <v>-0.06330475302183551</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1949601856424185</v>
+        <v>-0.06215380107152317</v>
       </c>
       <c r="Q7" t="n">
         <v>0.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9109479065754451</v>
+        <v>0.9412633743948358</v>
       </c>
       <c r="S7" t="n">
-        <v>1.507418699722411</v>
+        <v>1.45886533231984</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5581530345707558</v>
+        <v>-0.5686916882663008</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2717447010867484</v>
+        <v>0.2919173603330786</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1440592220234972</v>
+        <v>0.1832086639959698</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.2878151733554178</v>
+        <v>-0.2905418169901592</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3266168621082502</v>
+        <v>0.20623652882651</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3691407672367993</v>
+        <v>0.371755016125575</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5552670151495775</v>
+        <v>0.5543573724840594</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.202214317360971</v>
+        <v>1.182641430526517</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.393841537583128</v>
+        <v>0.399214939794564</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3759759178706343</v>
+        <v>0.3874042033122166</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.1005519359293524</v>
+        <v>-0.1101471637758638</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.35095197858634</v>
+        <v>-0.3404062664995018</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2099904218452131</v>
+        <v>0.06214046238739496</v>
       </c>
       <c r="AG7" t="n">
         <v>0.1</v>
@@ -1497,43 +1497,43 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.08596338392787</v>
+        <v>1.076952845877252</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.04430823730361991</v>
+        <v>0.03435810745920628</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.615830442686725</v>
+        <v>0.6189449694203462</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.365053153782079</v>
+        <v>0.3770317311948003</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.2022905364541907</v>
+        <v>-0.2094659376441372</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.02817087618226948</v>
+        <v>0.02979053331640268</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.24724377293904</v>
+        <v>0.2459632499593471</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.7363249806728099</v>
+        <v>0.7387951571157307</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.327701184492657</v>
+        <v>1.322787733345802</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.04412951245625466</v>
+        <v>0.02101975324279248</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.3079190777798948</v>
+        <v>0.3313900348760164</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.01122762548071386</v>
+        <v>0.0106530618286418</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.2216085290280233</v>
+        <v>-0.2259296935389085</v>
       </c>
     </row>
     <row r="8">
@@ -1549,136 +1549,136 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2992509051412833</v>
+        <v>0.2974254980535456</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2158747015562565</v>
+        <v>0.2163686520806584</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>122.8486493047839</v>
+        <v>129.6401246559499</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1796838742040784</v>
+        <v>0.07444807550373769</v>
       </c>
       <c r="I8" t="n">
-        <v>0.270707417948533</v>
+        <v>0.2591479962057969</v>
       </c>
       <c r="J8" t="n">
         <v>0.9999999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>1.036744070279867</v>
+        <v>1.042000877256893</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6483435775649027</v>
+        <v>0.6288853174818195</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1632055079175866</v>
+        <v>0.1814149285705289</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0414370981888544</v>
+        <v>-0.07793507636003187</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.06543785149342873</v>
+        <v>-0.05606147920215514</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2072000631777318</v>
+        <v>-0.1117125558150089</v>
       </c>
       <c r="Q8" t="n">
         <v>0.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.965833214497681</v>
+        <v>0.9999999999992916</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8990626441229024</v>
+        <v>0.8727664842628914</v>
       </c>
       <c r="T8" t="n">
-        <v>0.405172173335783</v>
+        <v>0.3722330482761068</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4555159392737612</v>
+        <v>0.4503556030107644</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02022908454327135</v>
+        <v>0.0430925416567872</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1303836601637559</v>
+        <v>0.1186469144882184</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.116910791527187</v>
+        <v>-0.03250200362204575</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5454692397552984</v>
+        <v>0.5402850668446317</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6888635416376145</v>
+        <v>0.695603490124742</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8282323766196572</v>
+        <v>0.8317443123982675</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7343074969543264</v>
+        <v>0.7436706909024118</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.4975533080644082</v>
+        <v>0.4933068241321426</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.1076974606599141</v>
+        <v>0.1055344428787883</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.0447678504361424</v>
+        <v>-0.04635380075404588</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.2675194232814939</v>
+        <v>0.1942262547735315</v>
       </c>
       <c r="AG8" t="n">
         <v>0.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.9865573358698637</v>
+        <v>0.9999999999996306</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.7038672412535736</v>
+        <v>0.693498480088422</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.08050870074578842</v>
+        <v>0.07986593007380759</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.6263193081909706</v>
+        <v>0.6272085133105165</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.06855321697535095</v>
+        <v>-0.0651859764733871</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.08392341316520727</v>
+        <v>0.0769517517605556</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.03077311069516336</v>
+        <v>0.03111494271005363</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.2540441644259578</v>
+        <v>0.2498582657626071</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.9103135230012898</v>
+        <v>0.923900872530916</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.8669765830689999</v>
+        <v>0.8600025385016185</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.4670829871502001</v>
+        <v>0.4561637466835364</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.4356485158616816</v>
+        <v>0.4380714672559881</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.004484057509745031</v>
+        <v>0.001376482925539133</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.02602534284984802</v>
+        <v>0.02329584657314326</v>
       </c>
     </row>
   </sheetData>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="n">
         <v>0.03</v>
@@ -1818,10 +1818,10 @@
         <v>1.5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3051968666182154</v>
+        <v>0.3057733772379714</v>
       </c>
       <c r="L2" t="n">
-        <v>93.47608427185396</v>
+        <v>101.6598481905929</v>
       </c>
       <c r="M2" t="n">
         <v>357</v>
@@ -1875,10 +1875,10 @@
         <v>1.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3707508200438505</v>
+        <v>0.3718301097921195</v>
       </c>
       <c r="L3" t="n">
-        <v>80.27893325057785</v>
+        <v>80.45317604419407</v>
       </c>
       <c r="M3" t="n">
         <v>315</v>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
         <v>0.03</v>
@@ -1932,10 +1932,10 @@
         <v>1.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3310878607431203</v>
+        <v>0.3191558333401444</v>
       </c>
       <c r="L4" t="n">
-        <v>86.04486932845839</v>
+        <v>84.38103502258883</v>
       </c>
       <c r="M4" t="n">
         <v>371</v>
@@ -1989,10 +1989,10 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3135192462715628</v>
+        <v>0.3141707001936448</v>
       </c>
       <c r="L5" t="n">
-        <v>78.42929246567445</v>
+        <v>78.4474054106777</v>
       </c>
       <c r="M5" t="n">
         <v>322</v>

--- a/01_Thermal/B_results/four_annular_bemt_params.xlsx
+++ b/01_Thermal/B_results/four_annular_bemt_params.xlsx
@@ -679,136 +679,136 @@
         <v>195</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3070871685863056</v>
+        <v>0.3086595877206444</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2329940927529772</v>
+        <v>0.2335690554157923</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>110.6049197342154</v>
+        <v>60.27571079561734</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.06842895636174645</v>
+        <v>-0.04064655724799168</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3001362884761485</v>
+        <v>0.2994594642258604</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1699654550637675</v>
+        <v>0.1705503211023353</v>
       </c>
       <c r="K2" t="n">
-        <v>7.698296625876307</v>
+        <v>7.731764986351314</v>
       </c>
       <c r="L2" t="n">
-        <v>1.227554585639528</v>
+        <v>1.235265973435096</v>
       </c>
       <c r="M2" t="n">
-        <v>1.24614447181849</v>
+        <v>1.254097714253479</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7961853351143451</v>
+        <v>-0.7994236447176373</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0144241030577102</v>
+        <v>-0.003274326790653231</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02239733392807139</v>
+        <v>0.009825278899024037</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2917410565696216</v>
+        <v>0.2975512106968374</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1605031521305101</v>
+        <v>0.1521504898125229</v>
       </c>
       <c r="S2" t="n">
-        <v>8.044499999999999</v>
+        <v>8.044499999999992</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3520157995638803</v>
+        <v>-0.3289821783693488</v>
       </c>
       <c r="U2" t="n">
-        <v>1.875215550250575</v>
+        <v>1.844440571097681</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.05191301037765998</v>
+        <v>-0.04711963951631461</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.985262479644983</v>
+        <v>-0.3127836733473268</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1784362989155303</v>
+        <v>0.1645754541269392</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2944144400703275</v>
+        <v>0.2956700369397927</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1616404017315249</v>
+        <v>0.1600802547796232</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.100250000000001</v>
+        <v>9.100249999990661</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.578903461170347</v>
+        <v>1.551106261959442</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.145601909398014</v>
+        <v>1.129779132375724</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.7627995608634331</v>
+        <v>-0.7332425842118248</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.35323621614967</v>
+        <v>-0.1804463179284478</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1827903683534494</v>
+        <v>0.1699087180118347</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.2986595139527869</v>
+        <v>0.2994508704449922</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.1546777428958966</v>
+        <v>0.1538667615751182</v>
       </c>
       <c r="AI2" t="n">
-        <v>8.354593749999998</v>
+        <v>8.354593749997106</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-1.815268541960138</v>
+        <v>-1.811447023655292</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.5215832373007344</v>
+        <v>0.5213496202663143</v>
       </c>
       <c r="AL2" t="n">
-        <v>-1.045682755365054</v>
+        <v>-1.043434739752075</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.2250919973833315</v>
+        <v>0.2823463294218323</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.07879876120882615</v>
+        <v>0.07591572344745157</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.2962378247672212</v>
+        <v>0.2980328955768706</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.1616966879554247</v>
+        <v>0.1591619568173999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.299410093969076</v>
+        <v>8.307777184084769</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.159793426321464</v>
+        <v>0.1614857583424744</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.197136292191953</v>
+        <v>1.1874167594983</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0.664145165430123</v>
+        <v>-0.6558051520494629</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.5247456488384029</v>
+        <v>-0.05353949716114888</v>
       </c>
     </row>
     <row r="3">
@@ -824,136 +824,136 @@
         <v>195</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5490400540866132</v>
+        <v>0.3448157727013739</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2880298744474953</v>
+        <v>0.2554055122026643</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>157.8341079908381</v>
+        <v>67.76646821357264</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04870439806472449</v>
+        <v>0.06731524245030368</v>
       </c>
       <c r="I3" t="n">
-        <v>0.649999999999842</v>
+        <v>0.3352314163739459</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9999999999999999</v>
+        <v>0.3675106961965422</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5260619256701073</v>
+        <v>2.700730793756347</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1895321978620723</v>
+        <v>-0.4926225745875933</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5192199233857774</v>
+        <v>0.2558665065718545</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.09147439392544279</v>
+        <v>0.6021330711637595</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06565522357566832</v>
+        <v>-0.5319531355067096</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9186141825415e-05</v>
+        <v>0.01770264136232418</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3509691552645023</v>
+        <v>0.3562440352166454</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2685048222262671</v>
+        <v>0.2840892483009383</v>
       </c>
       <c r="S3" t="n">
-        <v>2.861329990464961</v>
+        <v>2.76765910103407</v>
       </c>
       <c r="T3" t="n">
-        <v>0.188313483819213</v>
+        <v>0.01201683856524856</v>
       </c>
       <c r="U3" t="n">
-        <v>1.068207568454569</v>
+        <v>0.8172304923436596</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8629541558750187</v>
+        <v>0.8146719929663823</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6775048646047581</v>
+        <v>-0.3432379930107695</v>
       </c>
       <c r="X3" t="n">
-        <v>0.032879926796039</v>
+        <v>0.05172271067416046</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2971995739471388</v>
+        <v>0.3076476464576471</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2253548110890088</v>
+        <v>0.2304445017558559</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.521932101865637</v>
+        <v>4.328443683080006</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.392302151050057</v>
+        <v>2.108810403607493</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.552402741438483</v>
+        <v>-0.4126258070816093</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.6866728036755009</v>
+        <v>-0.6440922504209021</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1.605084993173607</v>
+        <v>-0.8155480131357719</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1115245598798791</v>
+        <v>0.1317471918698267</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.30585904841714</v>
+        <v>0.3067229692272335</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.209028823955737</v>
+        <v>0.2032983655596355</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.767838431922064</v>
+        <v>4.714697948080623</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.8040014425619971</v>
+        <v>0.8151974690764494</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.269839472774124</v>
+        <v>1.28713479443947</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.6995203656974418</v>
+        <v>-0.7077326076832072</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.2617221742960592</v>
+        <v>0.3011932608025945</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.04828201772061699</v>
+        <v>0.06712194658915376</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.4010069444071557</v>
+        <v>0.326461516818868</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.4257221143177531</v>
+        <v>0.2713357029532429</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.169290612480692</v>
+        <v>3.627882881487762</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7987712198922987</v>
+        <v>0.6108505341653994</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.3166060941011081</v>
+        <v>0.4869014965683436</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.1536783518558417</v>
+        <v>0.0162450515065081</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.4888031149766594</v>
+        <v>-0.3473864702126642</v>
       </c>
     </row>
     <row r="4">
@@ -969,136 +969,136 @@
         <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4301367971180799</v>
+        <v>0.426998123794389</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2751283748604808</v>
+        <v>0.2747607789709179</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>147.3765820468469</v>
+        <v>93.84149608175777</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03195251585108323</v>
+        <v>0.04564166929719618</v>
       </c>
       <c r="I4" t="n">
-        <v>0.530353276964896</v>
+        <v>0.5267292565985783</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1982377252665156</v>
+        <v>0.1910689646951307</v>
       </c>
       <c r="K4" t="n">
-        <v>2.702335807052048</v>
+        <v>2.673942773171619</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7688965721173461</v>
+        <v>-0.779385643169026</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6421521201367134</v>
+        <v>0.7083667056770174</v>
       </c>
       <c r="N4" t="n">
-        <v>1.003108128305951</v>
+        <v>0.9798040430377548</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9254111613005507</v>
+        <v>-0.931856592393445</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01574686783800995</v>
+        <v>0.02928932629779648</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5268445675189075</v>
+        <v>0.5235150812277563</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1701482800039372</v>
+        <v>0.1577018961412505</v>
       </c>
       <c r="S4" t="n">
-        <v>2.831774172988569</v>
+        <v>2.814918033680377</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.738954794294159</v>
+        <v>-1.84697095129585</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6364772643415658</v>
+        <v>0.6745531284394326</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.08865051959931765</v>
+        <v>-0.1912510734420257</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7424448671069743</v>
+        <v>-0.7581218810631286</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1062284026969533</v>
+        <v>0.1206799499449536</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.2014133603286974</v>
+        <v>0.2384761307509675</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.4675518634689663</v>
+        <v>0.4210320528676934</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.784449877990022</v>
+        <v>2.68197665522169</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2830742588788154</v>
+        <v>0.3059906509342383</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.5374606145208538</v>
+        <v>-0.4424852565999924</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.8081309705386965</v>
+        <v>0.7483801199873467</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.8225210843523818</v>
+        <v>-0.6828221133906572</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.08005499494718549</v>
+        <v>0.0942141744818365</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3505921225656516</v>
+        <v>0.3432299512185804</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.3466393606972639</v>
+        <v>0.3237177539642206</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.360270708022261</v>
+        <v>2.355476570779888</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.783316351306331</v>
+        <v>0.8680668518277689</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.003090774787603614</v>
+        <v>-0.01701175026784609</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.1184011054814306</v>
+        <v>-0.1084432408721587</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.1844177269501827</v>
+        <v>0.2116965643171894</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.05849569533330798</v>
+        <v>0.07245628000544568</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.4023008318445381</v>
+        <v>0.4079876049489706</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.2956443073591707</v>
+        <v>0.2733801669170738</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.669707641513225</v>
+        <v>2.631578508213393</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.3603651890565896</v>
+        <v>-0.3630747729257171</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.1845194987924554</v>
+        <v>0.2308557068121529</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.4010468684409748</v>
+        <v>0.3571224621777293</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.5764898464524311</v>
+        <v>-0.5402760056325103</v>
       </c>
     </row>
     <row r="5">
@@ -1114,136 +1114,136 @@
         <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3896332152354891</v>
+        <v>0.3906605492925991</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2733502100677215</v>
+        <v>0.2718131022317115</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>385.1806509287684</v>
+        <v>202.3073988568334</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.04697826742415452</v>
+        <v>-0.1673271745061343</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5817449828792735</v>
+        <v>0.5850269902220993</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1987772928073513</v>
+        <v>0.1978869393406207</v>
       </c>
       <c r="K5" t="n">
-        <v>2.571756514364463</v>
+        <v>2.606739467626462</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5565046301214347</v>
+        <v>0.5956039305028459</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4686528063719399</v>
+        <v>0.4842122497955346</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02356478191824077</v>
+        <v>-0.09450352145395026</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8857909858311381</v>
+        <v>-0.8867279963311782</v>
       </c>
       <c r="P5" t="n">
-        <v>0.06492484461452371</v>
+        <v>0.09905061898002158</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5705076840304724</v>
+        <v>0.5758141909533907</v>
       </c>
       <c r="R5" t="n">
-        <v>0.182395619191287</v>
+        <v>0.1884764530787606</v>
       </c>
       <c r="S5" t="n">
-        <v>3.017032011213016</v>
+        <v>3.045066458995167</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3019601829109342</v>
+        <v>-0.3578582052729077</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7792059871203836</v>
+        <v>0.7097010926204478</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.332221102855063</v>
+        <v>-0.3686801296778511</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3611373218410147</v>
+        <v>-0.3731100866471825</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1476464777551237</v>
+        <v>0.1734392705257579</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3054450463325407</v>
+        <v>0.3107787181727585</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3763310596894388</v>
+        <v>0.3940111347531716</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.498908784840098</v>
+        <v>2.480390687481271</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.4675659321558129</v>
+        <v>-0.3842790233036895</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.1810597873812929</v>
+        <v>-0.1451313651944991</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.09530073602988956</v>
+        <v>0.07624885444410391</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.214878884257754</v>
+        <v>-0.08741893819099751</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.212011343987487</v>
+        <v>0.2383689501059677</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.5379096254521967</v>
+        <v>0.5409751666276762</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.1972662235239467</v>
+        <v>0.2050150846151892</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.511611782912897</v>
+        <v>2.529840487288087</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.8169395360281914</v>
+        <v>0.8099138160943476</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.08800072176236755</v>
+        <v>-0.05466684205086478</v>
       </c>
       <c r="AL5" t="n">
-        <v>-1.753006630734389</v>
+        <v>-1.685287785290612</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.3524947890427977</v>
+        <v>-0.3511090518039215</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.09440109973324498</v>
+        <v>0.08588291627640322</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.4989018346736208</v>
+        <v>0.5031487664939811</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.238692548803006</v>
+        <v>0.2463474029469355</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.649827273332618</v>
+        <v>2.665509275347747</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.1509795127707197</v>
+        <v>0.1658451295051491</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.2446995710871658</v>
+        <v>0.2485287837926546</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.5033729448694507</v>
+        <v>-0.5180556454945773</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.4535754952431761</v>
+        <v>-0.4245915182433199</v>
       </c>
     </row>
     <row r="6">
@@ -1259,136 +1259,136 @@
         <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4112383304357538</v>
+        <v>0.409740443497478</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2782458734513925</v>
+        <v>0.2777055050692207</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>221.6939679615793</v>
+        <v>183.2018856637225</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03665619029436355</v>
+        <v>0.0498114878384747</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3640394263967048</v>
+        <v>0.3523616323938488</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4774798223261441</v>
+        <v>0.4914207508217424</v>
       </c>
       <c r="K6" t="n">
-        <v>2.208653254787602</v>
+        <v>2.155095688576428</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4125149002120131</v>
+        <v>0.4830156518661732</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4302977856868854</v>
+        <v>0.4442421925926811</v>
       </c>
       <c r="N6" t="n">
-        <v>0.02455063375947884</v>
+        <v>0.04585459356152691</v>
       </c>
       <c r="O6" t="n">
-        <v>0.499856442280173</v>
+        <v>0.5293858945150098</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.085399255270665</v>
+        <v>-0.0722870665786059</v>
       </c>
       <c r="Q6" t="n">
         <v>0.15</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8824688199124172</v>
+        <v>0.7825774955940454</v>
       </c>
       <c r="S6" t="n">
-        <v>1.629271297174825</v>
+        <v>1.674688234368683</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6069085071965725</v>
+        <v>-0.6043499204997804</v>
       </c>
       <c r="U6" t="n">
-        <v>0.05526145088512934</v>
+        <v>-0.009590744711311274</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.438991577232705</v>
+        <v>-0.5582067510076669</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2363582224273399</v>
+        <v>-0.2091266137390287</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03080700172900964</v>
+        <v>0.04388807227073021</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5465280015438483</v>
+        <v>0.5461341055468415</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6239619128410973</v>
+        <v>0.5964207934203954</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.364526694067</v>
+        <v>1.322137183585141</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6700703158203796</v>
+        <v>0.6888993010398865</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.5251348125286727</v>
+        <v>0.5294731062088445</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.02999216641172034</v>
+        <v>-0.05338154622453556</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.2232918977743206</v>
+        <v>0.2520642032710685</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1513902738501608</v>
+        <v>0.1660015613201724</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.3489121585824726</v>
+        <v>0.3471827864005193</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.4008811375997733</v>
+        <v>0.3841155769999653</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.841418031077795</v>
+        <v>1.804795841292046</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.3747489219859632</v>
+        <v>0.395543905253515</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.1669356908802885</v>
+        <v>-0.1608103850484143</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.09242599838347854</v>
+        <v>-0.1052264736904152</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.4953172160437589</v>
+        <v>0.545316837649813</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.03336355265071725</v>
+        <v>0.04685351371269284</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.3523698966307564</v>
+        <v>0.3489196310853024</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.596197923169858</v>
+        <v>0.5636336542090372</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.760967319276805</v>
+        <v>1.739179236955574</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.2126064077054458</v>
+        <v>0.2407772344149486</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.2109395895550998</v>
+        <v>0.20082854226045</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.1342147770671062</v>
+        <v>-0.1677400443402727</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.2455268334177281</v>
+        <v>0.2794100804242157</v>
       </c>
     </row>
     <row r="7">
@@ -1404,91 +1404,91 @@
         <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2986364560272359</v>
+        <v>0.3023652899637788</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2048135103805745</v>
+        <v>0.2038179886688392</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>170.6804554918937</v>
+        <v>140.0562076494373</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.08706105687677107</v>
+        <v>-0.1191885929919295</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4120979837118133</v>
+        <v>0.4204007644173999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4595598815840282</v>
+        <v>0.4750745493417767</v>
       </c>
       <c r="K7" t="n">
-        <v>1.572691324659599</v>
+        <v>1.526204071706977</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2191976539837004</v>
+        <v>0.2776316072629948</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02729360643842402</v>
+        <v>-0.02924523552548002</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4074809841003392</v>
+        <v>-0.3789121885386105</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.06330475302183551</v>
+        <v>-0.05329590742841307</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.06215380107152317</v>
+        <v>-0.09180753306412182</v>
       </c>
       <c r="Q7" t="n">
         <v>0.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9412633743948358</v>
+        <v>0.9438308896624484</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45886533231984</v>
+        <v>1.444179859536496</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5686916882663008</v>
+        <v>-0.6085742640534552</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2919173603330786</v>
+        <v>0.3583735058279557</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1832086639959698</v>
+        <v>0.2148880936956373</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.2905418169901592</v>
+        <v>-0.280808893534516</v>
       </c>
       <c r="X7" t="n">
-        <v>0.20623652882651</v>
+        <v>0.2249673144398925</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.371755016125575</v>
+        <v>0.3691075540957414</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5543573724840594</v>
+        <v>0.5741108495858011</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.182641430526517</v>
+        <v>1.190642496532579</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.399214939794564</v>
+        <v>0.395758646090485</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.3874042033122166</v>
+        <v>0.3867606254971001</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.1101471637758638</v>
+        <v>-0.09706362922827567</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.3404062664995018</v>
+        <v>-0.319054096086693</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.06214046238739496</v>
+        <v>0.08900175612979561</v>
       </c>
       <c r="AG7" t="n">
         <v>0.1</v>
@@ -1497,43 +1497,43 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.076952845877252</v>
+        <v>1.102243047396106</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.03435810745920628</v>
+        <v>0.03897745560480956</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.6189449694203462</v>
+        <v>0.6082639867657169</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.3770317311948003</v>
+        <v>0.3561790980632815</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.2094659376441372</v>
+        <v>-0.2034492793840848</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.02979053331640268</v>
+        <v>0.0257432361284092</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.2459632499593471</v>
+        <v>0.2473770796282853</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.7387951571157307</v>
+        <v>0.7482540721475065</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.322787733345802</v>
+        <v>1.315817368793039</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.02101975324279248</v>
+        <v>0.02594836122620855</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.3313900348760164</v>
+        <v>0.3310382206413232</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0106530618286418</v>
+        <v>0.02377284349800815</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.2259296935389085</v>
+        <v>-0.2141520441084267</v>
       </c>
     </row>
     <row r="8">
@@ -1549,136 +1549,136 @@
         <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2974254980535456</v>
+        <v>0.2977076372154189</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2163686520806584</v>
+        <v>0.2164033134779284</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>129.6401246559499</v>
+        <v>132.4888388339292</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07444807550373769</v>
+        <v>0.07501497537075438</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2591479962057969</v>
+        <v>0.254968099132952</v>
       </c>
       <c r="J8" t="n">
         <v>0.9999999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>1.042000877256893</v>
+        <v>1.038891657341545</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6288853174818195</v>
+        <v>0.6668050514565692</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1814149285705289</v>
+        <v>0.2073845978990302</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.07793507636003187</v>
+        <v>-0.03904727779712269</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.05606147920215514</v>
+        <v>-0.05224013387913752</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1117125558150089</v>
+        <v>-0.1082378714660346</v>
       </c>
       <c r="Q8" t="n">
         <v>0.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9999999999992916</v>
+        <v>0.9569875594796321</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8727664842628914</v>
+        <v>0.8905057312490848</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3722330482761068</v>
+        <v>0.393038064906616</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4503556030107644</v>
+        <v>0.4345180534431962</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0430925416567872</v>
+        <v>0.03104741939577127</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1186469144882184</v>
+        <v>0.1100986164350537</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.03250200362204575</v>
+        <v>-0.03169507370979018</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5402850668446317</v>
+        <v>0.5555886339840016</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.695603490124742</v>
+        <v>0.676860421500912</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.8317443123982675</v>
+        <v>0.8052448667932715</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.7436706909024118</v>
+        <v>0.729245224119328</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.4933068241321426</v>
+        <v>0.5117169631969972</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.1055344428787883</v>
+        <v>0.1312343472649946</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.04635380075404588</v>
+        <v>-0.05506574426113939</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1942262547735315</v>
+        <v>0.2017776719894723</v>
       </c>
       <c r="AG8" t="n">
         <v>0.1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.9999999999996306</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.693498480088422</v>
+        <v>0.6935351596605771</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.07986593007380759</v>
+        <v>0.06491492208570196</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.6272085133105165</v>
+        <v>0.618516083145584</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.0651859764733871</v>
+        <v>-0.05424087370559472</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0769517517605556</v>
+        <v>0.1031372222069716</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.03111494271005363</v>
+        <v>0.03421492554610049</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.2498582657626071</v>
+        <v>0.2526391832792384</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.923900872530916</v>
+        <v>0.908461995245136</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.8600025385016185</v>
+        <v>0.8570443537611194</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.4561637466835364</v>
+        <v>0.4635008156420538</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.4380714672559881</v>
+        <v>0.4430339244212019</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001376482925539133</v>
+        <v>0.01724840378951211</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.02329584657314326</v>
+        <v>0.02648249012543709</v>
       </c>
     </row>
   </sheetData>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0.03</v>
@@ -1818,10 +1818,10 @@
         <v>1.5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3057733772379714</v>
+        <v>0.3234703379424175</v>
       </c>
       <c r="L2" t="n">
-        <v>101.6598481905929</v>
+        <v>91.45772269155313</v>
       </c>
       <c r="M2" t="n">
         <v>357</v>
@@ -1875,10 +1875,10 @@
         <v>1.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3718301097921195</v>
+        <v>0.3572355619017076</v>
       </c>
       <c r="L3" t="n">
-        <v>80.45317604419407</v>
+        <v>81.32623693228729</v>
       </c>
       <c r="M3" t="n">
         <v>315</v>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>0.03</v>
@@ -1932,10 +1932,10 @@
         <v>1.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3191558333401444</v>
+        <v>0.2874132785443332</v>
       </c>
       <c r="L4" t="n">
-        <v>84.38103502258883</v>
+        <v>86.93265446255245</v>
       </c>
       <c r="M4" t="n">
         <v>371</v>
@@ -1989,10 +1989,10 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3141707001936448</v>
+        <v>0.3216504793108857</v>
       </c>
       <c r="L5" t="n">
-        <v>78.4474054106777</v>
+        <v>78.31106084083663</v>
       </c>
       <c r="M5" t="n">
         <v>322</v>
